--- a/hall/resources/sample/AllianceShop.xlsx
+++ b/hall/resources/sample/AllianceShop.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -127,10 +127,10 @@
     <t>icon</t>
   </si>
   <si>
-    <t>1024001_1</t>
-  </si>
-  <si>
-    <t>能量</t>
+    <t>1024017_1</t>
+  </si>
+  <si>
+    <t>联盟任务补充券</t>
   </si>
   <si>
     <t>1024012_200</t>
@@ -148,22 +148,25 @@
     <t>研究点</t>
   </si>
   <si>
-    <t>1024008_1</t>
-  </si>
-  <si>
-    <t>雇员升级材料1</t>
-  </si>
-  <si>
-    <t>1024009_1</t>
-  </si>
-  <si>
-    <t>雇员升级材料2</t>
-  </si>
-  <si>
-    <t>1024010_1</t>
-  </si>
-  <si>
-    <t>雇员升级材料3</t>
+    <t>1024013_1</t>
+  </si>
+  <si>
+    <t>游客邀请函</t>
+  </si>
+  <si>
+    <t>1024014_1</t>
+  </si>
+  <si>
+    <t>雇员邀请函</t>
+  </si>
+  <si>
+    <t>1025404_1</t>
+  </si>
+  <si>
+    <t>紫色游客</t>
+  </si>
+  <si>
+    <t>1024012_4000</t>
   </si>
   <si>
     <t>1025506_1</t>
@@ -350,12 +353,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1497,13 +1500,13 @@
         <v>22</v>
       </c>
       <c r="E5" s="1">
-        <v>1024001</v>
+        <v>1024017</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
@@ -1590,7 +1593,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="1">
-        <v>1024008</v>
+        <v>1024013</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>30</v>
@@ -1621,7 +1624,7 @@
         <v>31</v>
       </c>
       <c r="E9" s="1">
-        <v>1024009</v>
+        <v>1024014</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>32</v>
@@ -1652,19 +1655,19 @@
         <v>33</v>
       </c>
       <c r="E10" s="1">
-        <v>1024010</v>
+        <v>1024404</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G10" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J10" s="2"/>
     </row>
@@ -1680,13 +1683,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1">
         <v>1025506</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -1695,7 +1698,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11" s="2"/>
     </row>
@@ -1711,13 +1714,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1">
         <v>1027401</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
@@ -1726,7 +1729,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J12" s="2"/>
     </row>

--- a/hall/resources/sample/AllianceShop.xlsx
+++ b/hall/resources/sample/AllianceShop.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
